--- a/marketing_report/outputs/Calidad_Datos/dominios_invalidos.xlsx
+++ b/marketing_report/outputs/Calidad_Datos/dominios_invalidos.xlsx
@@ -631,7 +631,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gmial.com</t>
+          <t>gmail.co</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -658,7 +658,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>gmail.co</t>
+          <t>gmial.com</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -874,12 +874,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>outlook.con</t>
+          <t>iclud.com</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>outlook.com</t>
+          <t>icloud.com</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -892,7 +892,7 @@
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>2.17</v>
+        <v>6.31</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>iclud.com</t>
+          <t>hotamil.com</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>icloud.com</t>
+          <t>hotmail.com</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -919,7 +919,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>6.31</v>
+        <v>1.19</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -928,12 +928,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hotamil.com</t>
+          <t>outlook.con</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hotmail.com</t>
+          <t>outlook.com</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -946,7 +946,7 @@
         <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>1.19</v>
+        <v>2.17</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -982,25 +982,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gmail.om</t>
+          <t>yahooo.com</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gmail.com</t>
+          <t>yahoo.com</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
       <c r="F21" t="n">
-        <v>3.67</v>
+        <v>2.06</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1009,25 +1009,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>yahooo.com</t>
+          <t>gmail.om</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yahoo.com</t>
+          <t>gmail.com</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>2.06</v>
+        <v>3.67</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1216,7 +1216,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gmail.i.comcom.com</t>
+          <t>sanluis.edu.ar</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1248,7 +1248,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sanluis.edu.ar</t>
+          <t>gmail.i.comcom.com</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1344,7 +1344,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gmail.comn</t>
+          <t>devnull.facebook.com</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1360,7 +1360,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>devnull.facebook.com</t>
+          <t>gmail.comn</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1440,7 +1440,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gmsil.com</t>
+          <t>gmail.comr</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1456,7 +1456,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>gmail.comr</t>
+          <t>gmsil.com</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1520,7 +1520,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gmail.comi</t>
+          <t>gmail.comcom</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1536,7 +1536,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gmail.comcom</t>
+          <t>gmail.comi</t>
         </is>
       </c>
       <c r="B31" t="n">
